--- a/data/trans_orig/P1403-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1403-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2007</t>
+          <t>Población con diagnóstico de hipertensión en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>39911</t>
+          <t>37442</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67686</t>
+          <t>66879</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21215</t>
+          <t>20601</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40925</t>
+          <t>40900</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64466</t>
+          <t>65560</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101768</t>
+          <t>97968</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406090</t>
+          <t>406897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>433865</t>
+          <t>436334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265755</t>
+          <t>265780</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285465</t>
+          <t>286079</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>678689</t>
+          <t>682489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>715991</t>
+          <t>714897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32946</t>
+          <t>33581</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56781</t>
+          <t>57902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,47%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13038</t>
+          <t>12502</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32208</t>
+          <t>30906</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>49864</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81560</t>
+          <t>81191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,99%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>310153</t>
+          <t>309032</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333988</t>
+          <t>333353</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>339657</t>
+          <t>340959</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>358827</t>
+          <t>359363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>657239</t>
+          <t>657608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>688970</t>
+          <t>688935</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56959</t>
+          <t>57248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>88568</t>
+          <t>89131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13872</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31553</t>
+          <t>31150</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75704</t>
+          <t>76277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111792</t>
+          <t>113159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453821</t>
+          <t>453258</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>485430</t>
+          <t>485141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136229</t>
+          <t>136632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153910</t>
+          <t>154567</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598379</t>
+          <t>597012</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>634467</t>
+          <t>633894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,26%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>188780</t>
+          <t>186972</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>235723</t>
+          <t>237691</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85855</t>
+          <t>85828</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>122273</t>
+          <t>121640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>282545</t>
+          <t>282881</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>347240</t>
+          <t>344846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1002611</t>
+          <t>1000643</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1049554</t>
+          <t>1051362</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>592012</t>
+          <t>592645</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>628430</t>
+          <t>628457</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1605380</t>
+          <t>1607774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1670075</t>
+          <t>1669739</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32201</t>
+          <t>31832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56633</t>
+          <t>56382</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70720</t>
+          <t>71637</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106584</t>
+          <t>108073</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111587</t>
+          <t>111310</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153881</t>
+          <t>155790</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>293922</t>
+          <t>294173</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>318354</t>
+          <t>318723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>462168</t>
+          <t>460679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>498032</t>
+          <t>497115</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>765426</t>
+          <t>763517</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>807720</t>
+          <t>807997</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>280814</t>
+          <t>283609</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>340569</t>
+          <t>342223</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>285993</t>
+          <t>283742</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>348324</t>
+          <t>348249</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287525</t>
+          <t>287769</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>908191</t>
+          <t>906537</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>967946</t>
+          <t>965151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1198636</t>
+          <t>1198711</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1260967</t>
+          <t>1263218</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,66%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>385647</t>
+          <t>389336</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>460384</t>
+          <t>465962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>532565</t>
+          <t>531370</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>617916</t>
+          <t>621870</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>941459</t>
+          <t>940964</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1059232</t>
+          <t>1054398</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2809806</t>
+          <t>2804228</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2884543</t>
+          <t>2880854</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,21%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2760208</t>
+          <t>2756254</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2845559</t>
+          <t>2846754</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5589082</t>
+          <t>5593916</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5706855</t>
+          <t>5707350</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2012</t>
+          <t>Población con diagnóstico de hipertensión en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>54284</t>
+          <t>55406</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>87498</t>
+          <t>88537</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19599</t>
+          <t>19766</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>43503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79893</t>
+          <t>81068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>120215</t>
+          <t>123057</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>349713</t>
+          <t>348674</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>382927</t>
+          <t>381805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272848</t>
+          <t>270951</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294855</t>
+          <t>294688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>631450</t>
+          <t>628608</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>671772</t>
+          <t>670597</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,21%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40095</t>
+          <t>40823</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67427</t>
+          <t>68493</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21598</t>
+          <t>22913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>46090</t>
+          <t>47226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68812</t>
+          <t>68086</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>103883</t>
+          <t>104970</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,87%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>351370</t>
+          <t>350304</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>378702</t>
+          <t>377974</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291921</t>
+          <t>290785</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316413</t>
+          <t>315098</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>652925</t>
+          <t>651838</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>687996</t>
+          <t>688722</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>111544</t>
+          <t>113947</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157041</t>
+          <t>158980</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45568</t>
+          <t>43541</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73012</t>
+          <t>71353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>169330</t>
+          <t>167139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220389</t>
+          <t>218259</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,54%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>472374</t>
+          <t>470435</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517871</t>
+          <t>515468</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>187117</t>
+          <t>188776</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>214561</t>
+          <t>216588</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>669155</t>
+          <t>671285</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>720214</t>
+          <t>722405</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,21%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>192516</t>
+          <t>197219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248538</t>
+          <t>252431</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67006</t>
+          <t>65654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105382</t>
+          <t>101502</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>272759</t>
+          <t>272153</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339197</t>
+          <t>339053</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,62%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>910471</t>
+          <t>906578</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>966493</t>
+          <t>961790</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>659340</t>
+          <t>663220</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>697716</t>
+          <t>699068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1584534</t>
+          <t>1584678</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1650972</t>
+          <t>1651578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,85%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77274</t>
+          <t>77116</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112718</t>
+          <t>112950</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168155</t>
+          <t>168521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>216366</t>
+          <t>219038</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>255639</t>
+          <t>257012</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>317319</t>
+          <t>318948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>397878</t>
+          <t>397646</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>433322</t>
+          <t>433480</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>543880</t>
+          <t>541208</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>592091</t>
+          <t>591725</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>953524</t>
+          <t>951895</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1015204</t>
+          <t>1013831</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9827</t>
+          <t>9303</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>315472</t>
+          <t>319107</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>377098</t>
+          <t>382606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>318000</t>
+          <t>319752</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>385071</t>
+          <t>384316</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>27,95%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257055</t>
+          <t>257579</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265874</t>
+          <t>265872</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>731145</t>
+          <t>725637</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>792771</t>
+          <t>789136</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,97%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>990054</t>
+          <t>990809</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1057125</t>
+          <t>1055373</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>72,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>76,75%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>527563</t>
+          <t>533306</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>624521</t>
+          <t>625679</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>689617</t>
+          <t>698838</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>788694</t>
+          <t>795089</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1249263</t>
+          <t>1251188</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1386131</t>
+          <t>1384400</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2797389</t>
+          <t>2796231</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2894347</t>
+          <t>2888604</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2757112</t>
+          <t>2750717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2856189</t>
+          <t>2846968</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5581585</t>
+          <t>5583316</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5718453</t>
+          <t>5716528</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2016</t>
+          <t>Población con diagnóstico de hipertensión en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44239</t>
+          <t>44189</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73843</t>
+          <t>72981</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19478</t>
+          <t>19688</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43200</t>
+          <t>45100</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68767</t>
+          <t>69251</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108153</t>
+          <t>108116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,7 +6088,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>355249</t>
+          <t>356111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384853</t>
+          <t>384903</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>303855</t>
+          <t>301955</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>327577</t>
+          <t>327367</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>667994</t>
+          <t>668031</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>707380</t>
+          <t>706896</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>42211</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71491</t>
+          <t>70823</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21119</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44811</t>
+          <t>44780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69557</t>
+          <t>70980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>106936</t>
+          <t>107119</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,29%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>305736</t>
+          <t>306404</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333544</t>
+          <t>335016</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327462</t>
+          <t>327493</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351154</t>
+          <t>351543</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>642564</t>
+          <t>642381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>679943</t>
+          <t>678520</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69110</t>
+          <t>69664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100826</t>
+          <t>102520</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22959</t>
+          <t>23987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>47490</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99981</t>
+          <t>99501</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140110</t>
+          <t>140361</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>421088</t>
+          <t>419394</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452804</t>
+          <t>452250</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119737</t>
+          <t>118633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143164</t>
+          <t>142136</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,18%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547926</t>
+          <t>547675</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588055</t>
+          <t>588535</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,54%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>185759</t>
+          <t>188107</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>238508</t>
+          <t>239645</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74789</t>
+          <t>75375</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112771</t>
+          <t>112123</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>275628</t>
+          <t>273603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>335938</t>
+          <t>337680</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,09%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>911130</t>
+          <t>909993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>963879</t>
+          <t>961531</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>713105</t>
+          <t>713753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>751087</t>
+          <t>750501</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1639576</t>
+          <t>1637834</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1699886</t>
+          <t>1701911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84486</t>
+          <t>84552</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121832</t>
+          <t>121658</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121250</t>
+          <t>120501</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>164166</t>
+          <t>163201</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>216547</t>
+          <t>214479</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273622</t>
+          <t>272771</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>498874</t>
+          <t>499048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>536220</t>
+          <t>536154</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>574078</t>
+          <t>575043</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>616994</t>
+          <t>617743</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1085328</t>
+          <t>1086179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1142403</t>
+          <t>1144471</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>267297</t>
+          <t>262887</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>329170</t>
+          <t>329186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,7 +7768,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>268219</t>
+          <t>265148</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>333953</t>
+          <t>333914</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,7 +7803,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279882</t>
+          <t>279790</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>752855</t>
+          <t>752839</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>814728</t>
+          <t>819138</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7886,7 +7886,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>75,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1035217</t>
+          <t>1035256</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1100951</t>
+          <t>1104022</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,63%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>473033</t>
+          <t>474831</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>554256</t>
+          <t>558219</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>576722</t>
+          <t>575339</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>675189</t>
+          <t>669301</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1073418</t>
+          <t>1073340</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1200008</t>
+          <t>1199303</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2831466</t>
+          <t>2827503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2912689</t>
+          <t>2910891</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2856407</t>
+          <t>2862295</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2954874</t>
+          <t>2956257</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5717310</t>
+          <t>5718015</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5843900</t>
+          <t>5843978</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de hipertensión en 2023</t>
+          <t>Población con diagnóstico de hipertensión en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>90152</t>
+          <t>89270</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123670</t>
+          <t>122761</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45224</t>
+          <t>45097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67521</t>
+          <t>66965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>139949</t>
+          <t>141330</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180895</t>
+          <t>180242</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,94%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380363</t>
+          <t>381272</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413881</t>
+          <t>414763</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,11%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>379946</t>
+          <t>380502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>402243</t>
+          <t>402370</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>770605</t>
+          <t>771258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811551</t>
+          <t>810170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80681</t>
+          <t>80314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113190</t>
+          <t>111707</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40072</t>
+          <t>40060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60152</t>
+          <t>58758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127589</t>
+          <t>128325</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>164178</t>
+          <t>163953</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>339023</t>
+          <t>340506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371532</t>
+          <t>371899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>321165</t>
+          <t>322559</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341245</t>
+          <t>341257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>669352</t>
+          <t>669577</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705941</t>
+          <t>705205</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,6%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33171</t>
+          <t>34727</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148100</t>
+          <t>150664</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33376</t>
+          <t>33315</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48920</t>
+          <t>50258</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>30,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55142</t>
+          <t>50523</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193349</t>
+          <t>190835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>519445</t>
+          <t>516881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634374</t>
+          <t>632818</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117372</t>
+          <t>116034</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132916</t>
+          <t>132977</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>69,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640488</t>
+          <t>643002</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>778695</t>
+          <t>783314</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>195475</t>
+          <t>197569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>245522</t>
+          <t>247329</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148049</t>
+          <t>148163</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>624801</t>
+          <t>640961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>370287</t>
+          <t>368473</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>951386</t>
+          <t>970991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>48,28%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>787940</t>
+          <t>786133</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>837987</t>
+          <t>835893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>352700</t>
+          <t>336540</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>829452</t>
+          <t>829338</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1059577</t>
+          <t>1039972</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1640676</t>
+          <t>1642490</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83812</t>
+          <t>81298</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117658</t>
+          <t>115588</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159253</t>
+          <t>162609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>248114</t>
+          <t>251813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>263268</t>
+          <t>252164</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>349073</t>
+          <t>344869</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,28%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>356391</t>
+          <t>358461</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>390237</t>
+          <t>392751</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>590355</t>
+          <t>586656</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>679216</t>
+          <t>675860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>69,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>963445</t>
+          <t>967649</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1049250</t>
+          <t>1060354</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>1895</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9668</t>
+          <t>9781</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>205396</t>
+          <t>204980</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>246151</t>
+          <t>245021</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>208168</t>
+          <t>207297</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>251634</t>
+          <t>252649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230839</t>
+          <t>230726</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238431</t>
+          <t>238612</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>514143</t>
+          <t>515273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>554898</t>
+          <t>555314</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>749167</t>
+          <t>748152</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>792633</t>
+          <t>793504</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>462143</t>
+          <t>468011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>676589</t>
+          <t>678813</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>732180</t>
+          <t>729688</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1426067</t>
+          <t>1482699</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,17 +10761,17 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1525052</t>
+          <t>1525053</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1327110</t>
+          <t>1318106</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2277027</t>
+          <t>2147635</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2695219</t>
+          <t>2692995</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2909665</t>
+          <t>2903797</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2145272</t>
+          <t>2088640</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2839159</t>
+          <t>2841651</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4666120</t>
+          <t>4795513</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5616037</t>
+          <t>5625042</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>81,02%</t>
         </is>
       </c>
     </row>
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6943147</t>
+          <t>6943148</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6943147</t>
+          <t>6943148</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6943147</t>
+          <t>6943148</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">

--- a/data/trans_orig/P1403-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1403-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>37442</t>
+          <t>39915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>66879</t>
+          <t>66863</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>20944</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40900</t>
+          <t>40828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>65560</t>
+          <t>66563</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97968</t>
+          <t>98923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>406897</t>
+          <t>406913</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>436334</t>
+          <t>433861</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>265780</t>
+          <t>265852</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>286079</t>
+          <t>285736</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>682489</t>
+          <t>681534</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>714897</t>
+          <t>713894</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33581</t>
+          <t>34209</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>57902</t>
+          <t>59629</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12078</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30906</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49864</t>
+          <t>49538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81191</t>
+          <t>82009</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>309032</t>
+          <t>307305</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333353</t>
+          <t>332725</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>340959</t>
+          <t>341040</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>359363</t>
+          <t>359787</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>657608</t>
+          <t>656790</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>688935</t>
+          <t>689261</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57248</t>
+          <t>56516</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>89131</t>
+          <t>87498</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>13202</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31150</t>
+          <t>31178</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76277</t>
+          <t>75014</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113159</t>
+          <t>111639</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>453258</t>
+          <t>454891</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>485141</t>
+          <t>485873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>136632</t>
+          <t>136604</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154567</t>
+          <t>154580</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>597012</t>
+          <t>598532</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>633894</t>
+          <t>635157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>186972</t>
+          <t>184737</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>237691</t>
+          <t>238633</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85828</t>
+          <t>83674</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121640</t>
+          <t>120120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>282881</t>
+          <t>283259</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>344846</t>
+          <t>345430</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1000643</t>
+          <t>999701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1051362</t>
+          <t>1053597</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>592645</t>
+          <t>594165</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>628457</t>
+          <t>630611</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1607774</t>
+          <t>1607190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1669739</t>
+          <t>1669361</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31832</t>
+          <t>32892</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56382</t>
+          <t>57055</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71637</t>
+          <t>71975</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108073</t>
+          <t>108060</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>111310</t>
+          <t>112629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155790</t>
+          <t>155363</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,9%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>294173</t>
+          <t>293500</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>318723</t>
+          <t>317663</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>460679</t>
+          <t>460692</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>497115</t>
+          <t>496777</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>763517</t>
+          <t>763944</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>807997</t>
+          <t>806678</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,75%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1769</t>
+          <t>1743</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10432</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>283609</t>
+          <t>284427</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>342223</t>
+          <t>344683</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>283742</t>
+          <t>284929</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>348249</t>
+          <t>348191</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>287769</t>
+          <t>287202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>296432</t>
+          <t>296458</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>906537</t>
+          <t>904077</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>965151</t>
+          <t>964333</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1198711</t>
+          <t>1198769</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1263218</t>
+          <t>1262031</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,58%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>389336</t>
+          <t>388085</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>465962</t>
+          <t>466267</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>531370</t>
+          <t>525019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>621870</t>
+          <t>615678</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>940964</t>
+          <t>939538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1054398</t>
+          <t>1061532</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,97%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2804228</t>
+          <t>2803923</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2880854</t>
+          <t>2882105</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2756254</t>
+          <t>2762446</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2846754</t>
+          <t>2853105</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5593916</t>
+          <t>5586782</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5707350</t>
+          <t>5708776</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,87%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>55406</t>
+          <t>54891</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88537</t>
+          <t>85798</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19766</t>
+          <t>19859</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43503</t>
+          <t>43644</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81068</t>
+          <t>79918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>123057</t>
+          <t>119811</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>348674</t>
+          <t>351413</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>381805</t>
+          <t>382320</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>270951</t>
+          <t>270810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>294688</t>
+          <t>294595</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>628608</t>
+          <t>631854</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>670597</t>
+          <t>671747</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,37%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40823</t>
+          <t>40650</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68493</t>
+          <t>67968</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>21960</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47226</t>
+          <t>46330</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68086</t>
+          <t>69418</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104970</t>
+          <t>107135</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>350304</t>
+          <t>350829</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>377974</t>
+          <t>378147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>290785</t>
+          <t>291681</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>315098</t>
+          <t>316051</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,03%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>651838</t>
+          <t>649673</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>688722</t>
+          <t>687390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,13%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>113947</t>
+          <t>115045</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158980</t>
+          <t>158445</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43541</t>
+          <t>44664</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71353</t>
+          <t>72364</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>167139</t>
+          <t>169294</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>218259</t>
+          <t>219952</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>470435</t>
+          <t>470970</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>515468</t>
+          <t>514370</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,9%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>188776</t>
+          <t>187765</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>216588</t>
+          <t>215465</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>671285</t>
+          <t>669592</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>722405</t>
+          <t>720250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,46%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,97%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197219</t>
+          <t>193632</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>252431</t>
+          <t>252867</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65654</t>
+          <t>64061</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101502</t>
+          <t>100867</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>272153</t>
+          <t>274686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339053</t>
+          <t>336608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>906578</t>
+          <t>906142</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>961790</t>
+          <t>965377</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,98%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>663220</t>
+          <t>663855</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>699068</t>
+          <t>700661</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1584678</t>
+          <t>1587123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1651578</t>
+          <t>1649045</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77116</t>
+          <t>76512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>112950</t>
+          <t>112170</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>168521</t>
+          <t>170284</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>219038</t>
+          <t>216567</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>257012</t>
+          <t>258045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>318948</t>
+          <t>319180</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>397646</t>
+          <t>398426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>433480</t>
+          <t>434084</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>541208</t>
+          <t>543679</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>591725</t>
+          <t>589962</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>951895</t>
+          <t>951663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1013831</t>
+          <t>1012798</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,69%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>993</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>319107</t>
+          <t>318556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>382606</t>
+          <t>377938</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>319752</t>
+          <t>316922</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>384316</t>
+          <t>382335</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>257579</t>
+          <t>256943</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>265872</t>
+          <t>265889</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>725637</t>
+          <t>730305</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>789136</t>
+          <t>789687</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>990809</t>
+          <t>992790</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1055373</t>
+          <t>1058203</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>72,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>76,95%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>533306</t>
+          <t>533853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>625679</t>
+          <t>628754</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>698838</t>
+          <t>690468</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>795089</t>
+          <t>792654</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1251188</t>
+          <t>1253848</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1384400</t>
+          <t>1390862</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2796231</t>
+          <t>2793156</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2888604</t>
+          <t>2888057</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2750717</t>
+          <t>2753152</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2846968</t>
+          <t>2855338</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5583316</t>
+          <t>5576854</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5716528</t>
+          <t>5713868</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,0%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44189</t>
+          <t>44114</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72981</t>
+          <t>74078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19688</t>
+          <t>20026</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45100</t>
+          <t>45071</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,7 +6053,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69251</t>
+          <t>70135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108116</t>
+          <t>106769</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,76%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356111</t>
+          <t>355014</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>384903</t>
+          <t>384978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>301955</t>
+          <t>301984</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>327367</t>
+          <t>327029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>668031</t>
+          <t>669378</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>706896</t>
+          <t>706012</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42211</t>
+          <t>42924</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70823</t>
+          <t>71055</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>20730</t>
+          <t>21324</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44780</t>
+          <t>45112</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70980</t>
+          <t>69937</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>107119</t>
+          <t>106855</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,26%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>306404</t>
+          <t>306172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335016</t>
+          <t>334303</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>327493</t>
+          <t>327161</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>351543</t>
+          <t>350949</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>642381</t>
+          <t>642645</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>678520</t>
+          <t>679563</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,67%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69664</t>
+          <t>70073</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>102520</t>
+          <t>102368</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23987</t>
+          <t>23403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47490</t>
+          <t>46156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99501</t>
+          <t>100781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>140361</t>
+          <t>142036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>419394</t>
+          <t>419546</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452250</t>
+          <t>451841</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118633</t>
+          <t>119967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142136</t>
+          <t>142720</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547675</t>
+          <t>546000</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>588535</t>
+          <t>587255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>188107</t>
+          <t>184493</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>239645</t>
+          <t>237622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75375</t>
+          <t>74705</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>112123</t>
+          <t>113124</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>273603</t>
+          <t>275860</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>337680</t>
+          <t>339675</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>909993</t>
+          <t>912016</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>961531</t>
+          <t>965145</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>713753</t>
+          <t>712752</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>750501</t>
+          <t>751171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1637834</t>
+          <t>1635839</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1701911</t>
+          <t>1699654</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,04%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84552</t>
+          <t>84756</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121658</t>
+          <t>121862</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120501</t>
+          <t>119829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163201</t>
+          <t>163889</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>214479</t>
+          <t>215931</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>272771</t>
+          <t>270546</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,91%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>499048</t>
+          <t>498844</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>536154</t>
+          <t>535950</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>575043</t>
+          <t>574355</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>617743</t>
+          <t>618415</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1086179</t>
+          <t>1088404</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1144471</t>
+          <t>1143019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,11%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7355</t>
+          <t>7700</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7738,7 +7738,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>262887</t>
+          <t>265656</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>329186</t>
+          <t>329969</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>265148</t>
+          <t>265802</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>333914</t>
+          <t>333690</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,37%</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>279790</t>
+          <t>279445</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>752839</t>
+          <t>752056</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>819138</t>
+          <t>816369</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1035256</t>
+          <t>1035480</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1104022</t>
+          <t>1103368</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,59%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>474831</t>
+          <t>469882</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>558219</t>
+          <t>557918</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>575339</t>
+          <t>581907</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>669301</t>
+          <t>685309</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1073340</t>
+          <t>1078587</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1199303</t>
+          <t>1204819</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,42%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2827503</t>
+          <t>2827804</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2910891</t>
+          <t>2915840</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2862295</t>
+          <t>2846287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2956257</t>
+          <t>2949689</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5718015</t>
+          <t>5712499</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5843978</t>
+          <t>5838731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,41%</t>
         </is>
       </c>
     </row>
@@ -8633,32 +8633,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>106158</t>
+          <t>114897</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89270</t>
+          <t>97013</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122761</t>
+          <t>133701</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,32 +8668,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>54841</t>
+          <t>62982</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45097</t>
+          <t>51205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>66965</t>
+          <t>76244</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,32 +8703,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>160999</t>
+          <t>177879</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>141330</t>
+          <t>155371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>180242</t>
+          <t>200001</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -8746,32 +8746,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>397875</t>
+          <t>433376</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>381272</t>
+          <t>414572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>414763</t>
+          <t>451260</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8781,32 +8781,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>392626</t>
+          <t>425429</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>380502</t>
+          <t>412167</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>402370</t>
+          <t>437206</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8816,32 +8816,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>790501</t>
+          <t>858804</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>771258</t>
+          <t>836682</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>810170</t>
+          <t>881312</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,01%</t>
         </is>
       </c>
     </row>
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504033</t>
+          <t>548273</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504033</t>
+          <t>548273</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504033</t>
+          <t>548273</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>951500</t>
+          <t>1036683</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>951500</t>
+          <t>1036683</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>951500</t>
+          <t>1036683</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>95786</t>
+          <t>103506</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>80314</t>
+          <t>87381</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111707</t>
+          <t>121280</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49080</t>
+          <t>58007</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>47524</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>58758</t>
+          <t>69798</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>144866</t>
+          <t>161513</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>128325</t>
+          <t>142335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>163953</t>
+          <t>182904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>20,21%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>356427</t>
+          <t>379706</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>340506</t>
+          <t>361932</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371899</t>
+          <t>395831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>78,82%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,24%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>332237</t>
+          <t>363879</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>322559</t>
+          <t>352088</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>341257</t>
+          <t>374362</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>688664</t>
+          <t>743585</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>669577</t>
+          <t>722194</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>705205</t>
+          <t>762763</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,27%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>381317</t>
+          <t>421886</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>381317</t>
+          <t>421886</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>381317</t>
+          <t>421886</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>833530</t>
+          <t>905098</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>833530</t>
+          <t>905098</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>833530</t>
+          <t>905098</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>89357</t>
+          <t>98239</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>83626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>150664</t>
+          <t>116841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40572</t>
+          <t>45076</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>33315</t>
+          <t>36020</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50258</t>
+          <t>53809</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>129929</t>
+          <t>143316</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>50523</t>
+          <t>125947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>190835</t>
+          <t>163788</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>24,91%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>578188</t>
+          <t>372504</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516881</t>
+          <t>353902</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632818</t>
+          <t>387117</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,43%</t>
+          <t>75,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>125720</t>
+          <t>141746</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116034</t>
+          <t>133013</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>132977</t>
+          <t>150802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>703908</t>
+          <t>514250</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643002</t>
+          <t>493778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>783314</t>
+          <t>531619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>80,85%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>667545</t>
+          <t>470743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166292</t>
+          <t>186822</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>833837</t>
+          <t>657566</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>833837</t>
+          <t>657566</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>833837</t>
+          <t>657566</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>219547</t>
+          <t>237354</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>197569</t>
+          <t>212144</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>247329</t>
+          <t>266126</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>326806</t>
+          <t>133723</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148163</t>
+          <t>116945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>640961</t>
+          <t>150686</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>546353</t>
+          <t>371077</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>368473</t>
+          <t>340002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>970991</t>
+          <t>399192</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,28%</t>
+          <t>20,05%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>813915</t>
+          <t>892925</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>786133</t>
+          <t>864153</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>835893</t>
+          <t>918135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>79,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,88%</t>
+          <t>81,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>650695</t>
+          <t>726880</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>336540</t>
+          <t>709917</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>829338</t>
+          <t>743658</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1464610</t>
+          <t>1619805</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1039972</t>
+          <t>1591690</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1642490</t>
+          <t>1650880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1033462</t>
+          <t>1130279</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1033462</t>
+          <t>1130279</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1033462</t>
+          <t>1130279</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977501</t>
+          <t>860603</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977501</t>
+          <t>860603</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977501</t>
+          <t>860603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2010963</t>
+          <t>1990882</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2010963</t>
+          <t>1990882</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2010963</t>
+          <t>1990882</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>98128</t>
+          <t>106797</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81298</t>
+          <t>89796</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>115588</t>
+          <t>125405</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>215293</t>
+          <t>230403</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>162609</t>
+          <t>210311</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>251813</t>
+          <t>250838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>313421</t>
+          <t>337200</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>252164</t>
+          <t>311464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>344869</t>
+          <t>362965</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,99%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>375921</t>
+          <t>460179</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>358461</t>
+          <t>441571</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>392751</t>
+          <t>477180</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>623176</t>
+          <t>599156</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>586656</t>
+          <t>578721</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>675860</t>
+          <t>619248</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>999097</t>
+          <t>1059335</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>967649</t>
+          <t>1033570</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1060354</t>
+          <t>1085071</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>74,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>474049</t>
+          <t>566976</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>838469</t>
+          <t>829559</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>838469</t>
+          <t>829559</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>838469</t>
+          <t>829559</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1312518</t>
+          <t>1396535</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1312518</t>
+          <t>1396535</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1312518</t>
+          <t>1396535</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10348,32 +10348,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4488</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1839</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9781</t>
+          <t>9934</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>224993</t>
+          <t>240986</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>204980</t>
+          <t>219654</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>245021</t>
+          <t>265124</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>229484</t>
+          <t>245474</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>207297</t>
+          <t>224280</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>252649</t>
+          <t>268659</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>24,87%</t>
         </is>
       </c>
     </row>
@@ -10461,32 +10461,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>236016</t>
+          <t>232740</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>230726</t>
+          <t>227294</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238612</t>
+          <t>235389</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>535301</t>
+          <t>602209</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>515273</t>
+          <t>578071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>555314</t>
+          <t>623541</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>771317</t>
+          <t>834949</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>748152</t>
+          <t>811764</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>793504</t>
+          <t>856143</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>75,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>79,24%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760294</t>
+          <t>843195</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1000801</t>
+          <t>1080423</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>613467</t>
+          <t>665280</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>468011</t>
+          <t>622977</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>678813</t>
+          <t>710247</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>911586</t>
+          <t>771178</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>729688</t>
+          <t>729195</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1482699</t>
+          <t>812205</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1525053</t>
+          <t>1436458</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1318106</t>
+          <t>1378074</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2147635</t>
+          <t>1491308</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>2758341</t>
+          <t>2771430</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2692995</t>
+          <t>2726463</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2903797</t>
+          <t>2813733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>80,64%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>2659753</t>
+          <t>2859298</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2088640</t>
+          <t>2818271</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2841651</t>
+          <t>2901281</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>5418095</t>
+          <t>5630728</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>4795513</t>
+          <t>5575878</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5625042</t>
+          <t>5689112</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3371808</t>
+          <t>3436710</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3371808</t>
+          <t>3436710</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3371808</t>
+          <t>3436710</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3571339</t>
+          <t>3630476</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3571339</t>
+          <t>3630476</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3571339</t>
+          <t>3630476</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6943148</t>
+          <t>7067186</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6943148</t>
+          <t>7067186</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6943148</t>
+          <t>7067186</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
